--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:18:10+00:00</t>
+    <t>2023-04-28T11:24:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:24:11+00:00</t>
+    <t>2023-04-28T11:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:24:31+00:00</t>
+    <t>2023-04-30T03:44:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:44:40+00:00</t>
+    <t>2023-04-30T03:44:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:44:58+00:00</t>
+    <t>2023-04-30T03:52:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:52:18+00:00</t>
+    <t>2023-04-30T03:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:53:51+00:00</t>
+    <t>2023-04-30T09:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T09:28:44+00:00</t>
+    <t>2023-05-01T08:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T08:52:03+00:00</t>
+    <t>2023-05-01T08:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T08:56:42+00:00</t>
+    <t>2023-05-01T09:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:10:15+00:00</t>
+    <t>2023-05-01T09:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:11:26+00:00</t>
+    <t>2023-05-01T09:13:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:13:53+00:00</t>
+    <t>2023-05-01T09:16:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:16:45+00:00</t>
+    <t>2023-05-01T16:40:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T16:40:06+00:00</t>
+    <t>2023-05-01T16:40:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T16:40:27+00:00</t>
+    <t>2023-05-01T18:12:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:12:00+00:00</t>
+    <t>2023-05-01T18:12:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:12:07+00:00</t>
+    <t>2023-05-02T21:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:23:22+00:00</t>
+    <t>2023-05-02T21:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:27:47+00:00</t>
+    <t>2023-05-03T08:35:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:35:52+00:00</t>
+    <t>2023-05-03T08:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:46:45+00:00</t>
+    <t>2023-05-03T08:57:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:04+00:00</t>
+    <t>2023-05-03T08:57:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:52+00:00</t>
+    <t>2023-05-04T12:38:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:38:34+00:00</t>
+    <t>2023-05-04T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T21:01:51+00:00</t>
+    <t>2023-05-06T12:10:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3485,7 +3485,7 @@
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>182</v>
@@ -3986,13 +3986,13 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>80</v>
@@ -4109,7 +4109,7 @@
         <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>80</v>
@@ -4805,13 +4805,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>80</v>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:10:27+00:00</t>
+    <t>2023-05-06T12:11:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:11:33+00:00</t>
+    <t>2023-05-07T12:05:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:05:50+00:00</t>
+    <t>2023-05-07T12:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:06:01+00:00</t>
+    <t>2023-05-07T12:57:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:57:45+00:00</t>
+    <t>2023-05-07T12:58:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:58:10+00:00</t>
+    <t>2023-05-07T13:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:06:46+00:00</t>
+    <t>2023-05-07T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:07:20+00:00</t>
+    <t>2023-05-07T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:57:21+00:00</t>
+    <t>2023-05-08T06:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:13+00:00</t>
+    <t>2023-05-08T06:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:26+00:00</t>
+    <t>2023-05-08T13:44:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2161" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2160" uniqueCount="440">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -278,6 +278,9 @@
     <t>ClinicalDocument.recordTarget.patientRole</t>
   </si>
   <si>
+    <t>administrative.individual</t>
+  </si>
+  <si>
     <t>Patient.id</t>
   </si>
   <si>
@@ -361,7 +364,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -419,6 +422,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -469,6 +476,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>Patient.extension:PAY</t>
   </si>
   <si>
@@ -502,7 +513,7 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -601,70 +612,67 @@
     <t>Patient.name.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>Patient.name.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Patient.name.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this name.</t>
+  </si>
+  <si>
+    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/name-use|4.3.0</t>
+  </si>
+  <si>
+    <t>HumanName.use</t>
+  </si>
+  <si>
+    <t>unique(./use)</t>
+  </si>
+  <si>
+    <t>XPN.7, but often indicated by which field contains the name</t>
+  </si>
+  <si>
+    <t>Patient.name.text</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>Patient.name.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Patient.name.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this name.</t>
-  </si>
-  <si>
-    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>The use of a human name.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
-  </si>
-  <si>
-    <t>HumanName.use</t>
-  </si>
-  <si>
-    <t>unique(./use)</t>
-  </si>
-  <si>
-    <t>XPN.7, but often indicated by which field contains the name</t>
-  </si>
-  <si>
-    <t>Patient.name.text</t>
-  </si>
-  <si>
     <t>Text representation of the full name</t>
   </si>
   <si>
@@ -843,7 +851,7 @@
     <t>The gender of a person used for administrative purposes.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.3.0</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/administrativeGender</t>
@@ -1045,7 +1053,7 @@
     <t>Need to track people you can contact about the patient.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 pat-1:SHALL at least contain a contact's details or a reference to an organization {name.exists() or telecom.exists() or address.exists() or organization.exists()}</t>
   </si>
   <si>
@@ -1207,6 +1215,10 @@
   </si>
   <si>
     <t>If a patient does not speak the local language, interpreters may be required, so languages spoken and proficiency are important things to keep track of both for patient and other persons of interest.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
   </si>
   <si>
     <t>LanguageCommunication</t>
@@ -1375,7 +1387,7 @@
     <t>The type of link between this patient resource and another patient resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/link-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/link-type|4.3.0</t>
   </si>
   <si>
     <t>typeCode</t>
@@ -1971,7 +1983,7 @@
         <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>80</v>
@@ -1982,10 +1994,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1996,7 +2008,7 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>80</v>
@@ -2005,19 +2017,19 @@
         <v>80</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2067,13 +2079,13 @@
         <v>80</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>80</v>
@@ -2099,10 +2111,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2113,7 +2125,7 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>80</v>
@@ -2122,16 +2134,16 @@
         <v>80</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2182,19 +2194,19 @@
         <v>80</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>80</v>
@@ -2214,10 +2226,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2228,28 +2240,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2299,19 +2311,19 @@
         <v>80</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>80</v>
@@ -2331,10 +2343,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2345,7 +2357,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>80</v>
@@ -2357,16 +2369,16 @@
         <v>80</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2392,13 +2404,13 @@
         <v>80</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>80</v>
@@ -2416,19 +2428,19 @@
         <v>80</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>80</v>
@@ -2448,21 +2460,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>80</v>
@@ -2474,16 +2486,16 @@
         <v>80</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2533,22 +2545,22 @@
         <v>80</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>80</v>
@@ -2565,14 +2577,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2591,16 +2603,16 @@
         <v>80</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2650,7 +2662,7 @@
         <v>80</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2662,10 +2674,10 @@
         <v>80</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>80</v>
@@ -2682,10 +2694,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2708,13 +2720,13 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2753,17 +2765,17 @@
         <v>80</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2775,7 +2787,7 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>80</v>
@@ -2795,13 +2807,13 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>80</v>
@@ -2811,10 +2823,10 @@
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>80</v>
@@ -2823,13 +2835,13 @@
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2880,7 +2892,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2889,10 +2901,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>80</v>
@@ -2912,13 +2924,13 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>80</v>
@@ -2928,10 +2940,10 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>80</v>
@@ -2940,13 +2952,13 @@
         <v>80</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2997,7 +3009,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3006,10 +3018,10 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>80</v>
@@ -3029,14 +3041,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3049,25 +3061,25 @@
         <v>80</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -3116,7 +3128,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3128,10 +3140,10 @@
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>80</v>
@@ -3148,10 +3160,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3171,20 +3183,20 @@
         <v>80</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>80</v>
@@ -3233,7 +3245,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3245,19 +3257,19 @@
         <v>80</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>80</v>
@@ -3265,10 +3277,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3279,103 +3291,103 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="P14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="R14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH14" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="J14" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K14" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="P14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="R14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="AI14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>80</v>
@@ -3386,10 +3398,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3409,22 +3421,22 @@
         <v>80</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3473,7 +3485,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3488,16 +3500,16 @@
         <v>80</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>80</v>
@@ -3505,10 +3517,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3519,7 +3531,7 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>80</v>
@@ -3531,13 +3543,13 @@
         <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>186</v>
+        <v>90</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3588,13 +3600,13 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>80</v>
@@ -3603,7 +3615,7 @@
         <v>80</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>80</v>
@@ -3620,14 +3632,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3646,16 +3658,16 @@
         <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3693,19 +3705,19 @@
         <v>80</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3717,10 +3729,10 @@
         <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>80</v>
@@ -3737,10 +3749,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3751,31 +3763,31 @@
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -3800,13 +3812,11 @@
         <v>80</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>80</v>
@@ -3824,22 +3834,22 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>80</v>
@@ -3848,7 +3858,7 @@
         <v>80</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>80</v>
@@ -3856,10 +3866,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3870,7 +3880,7 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>80</v>
@@ -3879,22 +3889,22 @@
         <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -3943,22 +3953,22 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>80</v>
@@ -3967,7 +3977,7 @@
         <v>80</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>80</v>
@@ -3975,42 +3985,42 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4060,22 +4070,22 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>80</v>
@@ -4084,7 +4094,7 @@
         <v>80</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>80</v>
@@ -4092,42 +4102,42 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4177,7 +4187,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4189,10 +4199,10 @@
         <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>80</v>
@@ -4201,7 +4211,7 @@
         <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>80</v>
@@ -4209,10 +4219,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4232,16 +4242,16 @@
         <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4292,7 +4302,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4304,10 +4314,10 @@
         <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>80</v>
@@ -4316,7 +4326,7 @@
         <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>80</v>
@@ -4324,10 +4334,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4347,16 +4357,16 @@
         <v>80</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4407,7 +4417,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4419,10 +4429,10 @@
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>80</v>
@@ -4431,7 +4441,7 @@
         <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>80</v>
@@ -4439,10 +4449,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4453,7 +4463,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -4462,20 +4472,20 @@
         <v>80</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4524,22 +4534,22 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>80</v>
@@ -4548,7 +4558,7 @@
         <v>80</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>80</v>
@@ -4556,10 +4566,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4573,28 +4583,28 @@
         <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4643,7 +4653,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4655,19 +4665,19 @@
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>80</v>
@@ -4675,10 +4685,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4686,10 +4696,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>80</v>
@@ -4698,22 +4708,22 @@
         <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4738,13 +4748,13 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
@@ -4762,31 +4772,31 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>80</v>
@@ -4794,10 +4804,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4808,31 +4818,31 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -4881,42 +4891,42 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4927,31 +4937,31 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -5000,31 +5010,31 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>80</v>
@@ -5032,10 +5042,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5055,22 +5065,22 @@
         <v>80</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -5119,7 +5129,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5131,19 +5141,19 @@
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>80</v>
@@ -5151,10 +5161,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5165,7 +5175,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>80</v>
@@ -5177,17 +5187,17 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>80</v>
@@ -5212,13 +5222,13 @@
         <v>80</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>80</v>
@@ -5236,31 +5246,31 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>80</v>
@@ -5268,10 +5278,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5282,7 +5292,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>80</v>
@@ -5294,19 +5304,19 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -5355,31 +5365,31 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>80</v>
@@ -5387,10 +5397,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5413,19 +5423,19 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>80</v>
@@ -5474,7 +5484,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5486,19 +5496,19 @@
         <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>80</v>
@@ -5506,10 +5516,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5532,19 +5542,19 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5593,7 +5603,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5605,13 +5615,13 @@
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>80</v>
@@ -5625,10 +5635,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5639,7 +5649,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>80</v>
@@ -5651,13 +5661,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5708,13 +5718,13 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
@@ -5723,7 +5733,7 @@
         <v>80</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>80</v>
@@ -5740,14 +5750,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5766,16 +5776,16 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5825,7 +5835,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5837,10 +5847,10 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>80</v>
@@ -5857,14 +5867,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5877,25 +5887,25 @@
         <v>80</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -5944,7 +5954,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5956,10 +5966,10 @@
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>80</v>
@@ -5976,10 +5986,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6002,17 +6012,17 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6037,13 +6047,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6061,7 +6071,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6073,19 +6083,19 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
@@ -6093,10 +6103,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6107,7 +6117,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>80</v>
@@ -6119,17 +6129,17 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6178,31 +6188,31 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
@@ -6210,10 +6220,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6236,19 +6246,19 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6297,7 +6307,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6309,19 +6319,19 @@
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
@@ -6329,10 +6339,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6343,7 +6353,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>80</v>
@@ -6355,17 +6365,17 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6414,31 +6424,31 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>80</v>
@@ -6446,10 +6456,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6460,7 +6470,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -6472,17 +6482,17 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6507,13 +6517,13 @@
         <v>80</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>80</v>
@@ -6531,31 +6541,31 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>80</v>
@@ -6563,10 +6573,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6577,7 +6587,7 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -6589,17 +6599,17 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -6648,31 +6658,31 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
@@ -6680,10 +6690,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6694,7 +6704,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>80</v>
@@ -6706,13 +6716,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6763,25 +6773,25 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
@@ -6795,10 +6805,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6821,19 +6831,19 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -6882,7 +6892,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6894,13 +6904,13 @@
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>384</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
@@ -6914,10 +6924,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6928,7 +6938,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
@@ -6940,13 +6950,13 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6997,13 +7007,13 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
@@ -7012,7 +7022,7 @@
         <v>80</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>80</v>
@@ -7029,14 +7039,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7055,16 +7065,16 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7114,7 +7124,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7126,10 +7136,10 @@
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>80</v>
@@ -7146,14 +7156,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7166,25 +7176,25 @@
         <v>80</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7233,7 +7243,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7245,10 +7255,10 @@
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>80</v>
@@ -7265,10 +7275,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7276,10 +7286,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>80</v>
@@ -7291,19 +7301,19 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7328,13 +7338,13 @@
         <v>80</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>80</v>
@@ -7352,31 +7362,31 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>80</v>
@@ -7384,10 +7394,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7398,7 +7408,7 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>80</v>
@@ -7410,19 +7420,19 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7471,31 +7481,31 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>80</v>
@@ -7503,14 +7513,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7529,16 +7539,16 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7588,7 +7598,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7600,19 +7610,19 @@
         <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -7620,10 +7630,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7631,10 +7641,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>80</v>
@@ -7643,22 +7653,22 @@
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -7707,25 +7717,25 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>80</v>
@@ -7739,10 +7749,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7759,25 +7769,25 @@
         <v>80</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -7826,7 +7836,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7838,13 +7848,13 @@
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>99</v>
+        <v>384</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
@@ -7858,10 +7868,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7872,7 +7882,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>80</v>
@@ -7884,13 +7894,13 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7941,13 +7951,13 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>80</v>
@@ -7956,7 +7966,7 @@
         <v>80</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>80</v>
@@ -7973,14 +7983,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7999,16 +8009,16 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8058,7 +8068,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8070,10 +8080,10 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>80</v>
@@ -8090,14 +8100,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8110,25 +8120,25 @@
         <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8177,7 +8187,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8189,10 +8199,10 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>80</v>
@@ -8209,10 +8219,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8220,10 +8230,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>80</v>
@@ -8232,19 +8242,19 @@
         <v>80</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8294,31 +8304,31 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
@@ -8326,10 +8336,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8337,10 +8347,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>80</v>
@@ -8349,16 +8359,16 @@
         <v>80</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8385,49 +8395,49 @@
         <v>80</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="Z57" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="AA57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>432</v>
-      </c>
       <c r="AG57" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>80</v>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2160" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2161" uniqueCount="437">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -278,9 +278,6 @@
     <t>ClinicalDocument.recordTarget.patientRole</t>
   </si>
   <si>
-    <t>administrative.individual</t>
-  </si>
-  <si>
     <t>Patient.id</t>
   </si>
   <si>
@@ -364,7 +361,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -422,10 +419,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -476,10 +469,6 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
     <t>Patient.extension:PAY</t>
   </si>
   <si>
@@ -513,7 +502,7 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -612,67 +601,70 @@
     <t>Patient.name.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>Patient.name.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Patient.name.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this name.</t>
-  </si>
-  <si>
-    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/name-use|4.3.0</t>
-  </si>
-  <si>
-    <t>HumanName.use</t>
-  </si>
-  <si>
-    <t>unique(./use)</t>
-  </si>
-  <si>
-    <t>XPN.7, but often indicated by which field contains the name</t>
-  </si>
-  <si>
-    <t>Patient.name.text</t>
-  </si>
-  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>Patient.name.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Patient.name.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this name.</t>
+  </si>
+  <si>
+    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>The use of a human name.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
+  </si>
+  <si>
+    <t>HumanName.use</t>
+  </si>
+  <si>
+    <t>unique(./use)</t>
+  </si>
+  <si>
+    <t>XPN.7, but often indicated by which field contains the name</t>
+  </si>
+  <si>
+    <t>Patient.name.text</t>
+  </si>
+  <si>
     <t>Text representation of the full name</t>
   </si>
   <si>
@@ -851,7 +843,7 @@
     <t>The gender of a person used for administrative purposes.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/administrativeGender</t>
@@ -1053,7 +1045,7 @@
     <t>Need to track people you can contact about the patient.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 pat-1:SHALL at least contain a contact's details or a reference to an organization {name.exists() or telecom.exists() or address.exists() or organization.exists()}</t>
   </si>
   <si>
@@ -1215,10 +1207,6 @@
   </si>
   <si>
     <t>If a patient does not speak the local language, interpreters may be required, so languages spoken and proficiency are important things to keep track of both for patient and other persons of interest.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
   </si>
   <si>
     <t>LanguageCommunication</t>
@@ -1387,7 +1375,7 @@
     <t>The type of link between this patient resource and another patient resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/link-type|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/link-type|4.0.1</t>
   </si>
   <si>
     <t>typeCode</t>
@@ -1983,7 +1971,7 @@
         <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>80</v>
@@ -1994,10 +1982,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2008,28 +1996,28 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>93</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2079,13 +2067,13 @@
         <v>80</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>80</v>
@@ -2111,10 +2099,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2125,25 +2113,25 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2194,19 +2182,19 @@
         <v>80</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>80</v>
@@ -2226,10 +2214,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2240,28 +2228,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2311,19 +2299,19 @@
         <v>80</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>80</v>
@@ -2343,10 +2331,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2357,7 +2345,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>80</v>
@@ -2369,16 +2357,16 @@
         <v>80</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2404,43 +2392,43 @@
         <v>80</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>80</v>
@@ -2460,21 +2448,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>80</v>
@@ -2486,16 +2474,16 @@
         <v>80</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2545,22 +2533,22 @@
         <v>80</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK7" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>80</v>
@@ -2577,14 +2565,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2603,16 +2591,16 @@
         <v>80</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2662,7 +2650,7 @@
         <v>80</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2674,10 +2662,10 @@
         <v>80</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>80</v>
@@ -2694,10 +2682,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2720,13 +2708,13 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2765,17 +2753,17 @@
         <v>80</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2787,7 +2775,7 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>80</v>
@@ -2807,13 +2795,13 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>80</v>
@@ -2823,11 +2811,11 @@
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H10" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H10" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="I10" t="s" s="2">
         <v>80</v>
       </c>
@@ -2835,13 +2823,13 @@
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="L10" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2892,7 +2880,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2901,10 +2889,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>80</v>
@@ -2924,13 +2912,13 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>80</v>
@@ -2940,11 +2928,11 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H11" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H11" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="I11" t="s" s="2">
         <v>80</v>
       </c>
@@ -2952,13 +2940,13 @@
         <v>80</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3009,7 +2997,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3018,10 +3006,10 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>80</v>
@@ -3041,14 +3029,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3061,25 +3049,25 @@
         <v>80</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="O12" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -3128,7 +3116,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3140,10 +3128,10 @@
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>80</v>
@@ -3160,10 +3148,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3183,20 +3171,20 @@
         <v>80</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>80</v>
@@ -3245,7 +3233,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3257,19 +3245,19 @@
         <v>80</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>80</v>
@@ -3277,10 +3265,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3291,103 +3279,103 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I14" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J14" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="P14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="R14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK14" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="O14" t="s" s="2">
+      <c r="AL14" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="P14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="R14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>80</v>
@@ -3398,10 +3386,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3421,22 +3409,22 @@
         <v>80</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3485,7 +3473,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3500,16 +3488,16 @@
         <v>80</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>80</v>
@@ -3517,10 +3505,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3531,7 +3519,7 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>80</v>
@@ -3543,13 +3531,13 @@
         <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>90</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3600,13 +3588,13 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>80</v>
@@ -3615,7 +3603,7 @@
         <v>80</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>80</v>
@@ -3632,14 +3620,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3658,16 +3646,16 @@
         <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3705,19 +3693,19 @@
         <v>80</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3729,10 +3717,10 @@
         <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>80</v>
@@ -3749,10 +3737,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3763,31 +3751,31 @@
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I18" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J18" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -3812,53 +3800,55 @@
         <v>80</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="Z18" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="Y18" s="2"/>
-      <c r="Z18" t="s" s="2">
+      <c r="AA18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AA18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF18" t="s" s="2">
+      <c r="AG18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK18" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AG18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK18" t="s" s="2">
+      <c r="AL18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>80</v>
@@ -3866,10 +3856,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3880,31 +3870,31 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J19" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K19" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -3953,31 +3943,31 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>80</v>
@@ -3985,42 +3975,42 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H20" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="I20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4070,31 +4060,31 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>80</v>
@@ -4102,42 +4092,42 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4187,7 +4177,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4199,10 +4189,10 @@
         <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>80</v>
@@ -4211,7 +4201,7 @@
         <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>80</v>
@@ -4219,10 +4209,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4242,16 +4232,16 @@
         <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4302,7 +4292,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4314,10 +4304,10 @@
         <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>80</v>
@@ -4326,7 +4316,7 @@
         <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>80</v>
@@ -4334,10 +4324,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4357,16 +4347,16 @@
         <v>80</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4417,7 +4407,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4429,10 +4419,10 @@
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>80</v>
@@ -4441,7 +4431,7 @@
         <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>80</v>
@@ -4449,10 +4439,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4463,29 +4453,29 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K24" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4534,31 +4524,31 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>80</v>
@@ -4566,10 +4556,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4583,28 +4573,28 @@
         <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4653,7 +4643,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4665,19 +4655,19 @@
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>80</v>
@@ -4685,10 +4675,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4696,34 +4686,34 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G26" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K26" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4748,55 +4738,55 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK26" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="Z26" t="s" s="2">
+      <c r="AL26" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AA26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>80</v>
@@ -4804,10 +4794,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4818,31 +4808,31 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H27" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H27" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="I27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -4891,42 +4881,42 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>280</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4937,31 +4927,31 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I28" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="H28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J28" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -5010,31 +5000,31 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>80</v>
@@ -5042,10 +5032,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5065,22 +5055,22 @@
         <v>80</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -5129,7 +5119,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5141,19 +5131,19 @@
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>80</v>
@@ -5161,10 +5151,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5175,7 +5165,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>80</v>
@@ -5187,17 +5177,17 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>80</v>
@@ -5222,55 +5212,55 @@
         <v>80</v>
       </c>
       <c r="X30" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="Z30" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="Y30" t="s" s="2">
+      <c r="AA30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK30" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="Z30" t="s" s="2">
+      <c r="AL30" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AA30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>80</v>
@@ -5278,10 +5268,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5292,7 +5282,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>80</v>
@@ -5304,19 +5294,19 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -5365,31 +5355,31 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>80</v>
@@ -5397,10 +5387,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5423,19 +5413,19 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>80</v>
@@ -5484,7 +5474,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5496,19 +5486,19 @@
         <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>80</v>
@@ -5516,10 +5506,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5542,19 +5532,19 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5603,7 +5593,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5615,13 +5605,13 @@
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>80</v>
@@ -5635,10 +5625,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5649,7 +5639,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>80</v>
@@ -5661,13 +5651,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5718,13 +5708,13 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
@@ -5733,7 +5723,7 @@
         <v>80</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>80</v>
@@ -5750,14 +5740,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5776,16 +5766,16 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5835,7 +5825,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5847,10 +5837,10 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>80</v>
@@ -5867,14 +5857,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5887,25 +5877,25 @@
         <v>80</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -5954,7 +5944,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5966,10 +5956,10 @@
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>80</v>
@@ -5986,10 +5976,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6012,17 +6002,17 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6047,13 +6037,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6071,7 +6061,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6083,19 +6073,19 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
@@ -6103,10 +6093,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6117,7 +6107,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>80</v>
@@ -6129,17 +6119,17 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6188,31 +6178,31 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
@@ -6220,10 +6210,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6246,19 +6236,19 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M39" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>356</v>
-      </c>
       <c r="O39" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6307,7 +6297,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6319,19 +6309,19 @@
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
@@ -6339,10 +6329,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6353,7 +6343,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>80</v>
@@ -6365,17 +6355,17 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6424,31 +6414,31 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>80</v>
@@ -6456,10 +6446,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6470,7 +6460,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -6482,17 +6472,17 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6517,55 +6507,55 @@
         <v>80</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK41" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>268</v>
-      </c>
       <c r="AL41" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>80</v>
@@ -6573,10 +6563,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6587,7 +6577,7 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -6599,17 +6589,17 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -6658,31 +6648,31 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
@@ -6690,10 +6680,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6704,7 +6694,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>80</v>
@@ -6716,13 +6706,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6773,25 +6763,25 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
@@ -6805,10 +6795,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6831,19 +6821,19 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -6892,7 +6882,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6904,13 +6894,13 @@
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>384</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
@@ -6924,10 +6914,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6938,7 +6928,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
@@ -6950,13 +6940,13 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7007,13 +6997,13 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
@@ -7022,7 +7012,7 @@
         <v>80</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>80</v>
@@ -7039,14 +7029,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7065,16 +7055,16 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7124,7 +7114,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7136,10 +7126,10 @@
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>80</v>
@@ -7156,14 +7146,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7176,25 +7166,25 @@
         <v>80</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7243,7 +7233,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7255,10 +7245,10 @@
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>80</v>
@@ -7275,10 +7265,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7286,10 +7276,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>80</v>
@@ -7301,19 +7291,19 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7338,14 +7328,14 @@
         <v>80</v>
       </c>
       <c r="X48" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y48" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Y48" t="s" s="2">
+      <c r="Z48" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>114</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>80</v>
       </c>
@@ -7362,31 +7352,31 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>80</v>
@@ -7394,10 +7384,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7408,7 +7398,7 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>80</v>
@@ -7420,19 +7410,19 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="O49" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7481,31 +7471,31 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>80</v>
@@ -7513,14 +7503,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7539,16 +7529,16 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7598,7 +7588,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7610,19 +7600,19 @@
         <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -7630,10 +7620,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7641,34 +7631,34 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J51" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G51" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K51" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O51" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -7717,25 +7707,25 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>80</v>
@@ -7749,10 +7739,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7769,25 +7759,25 @@
         <v>80</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -7836,7 +7826,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7848,13 +7838,13 @@
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>384</v>
+        <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
@@ -7868,10 +7858,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7882,7 +7872,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>80</v>
@@ -7894,13 +7884,13 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7951,13 +7941,13 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>80</v>
@@ -7966,7 +7956,7 @@
         <v>80</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>80</v>
@@ -7983,14 +7973,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8009,16 +7999,16 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8068,7 +8058,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8080,10 +8070,10 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>80</v>
@@ -8100,14 +8090,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8120,25 +8110,25 @@
         <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8187,7 +8177,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8199,10 +8189,10 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>80</v>
@@ -8219,10 +8209,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8230,31 +8220,31 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J56" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G56" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K56" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8304,31 +8294,31 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
@@ -8336,10 +8326,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8347,28 +8337,28 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J57" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G57" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="K57" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8395,13 +8385,13 @@
         <v>80</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>80</v>
@@ -8419,25 +8409,25 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>80</v>

--- a/branches/Richard/StructureDefinition-hiv-patient.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
